--- a/data/export/coding/pareto_coding_frontier_story_data.xlsx
+++ b/data/export/coding/pareto_coding_frontier_story_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="frontier_only" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="weekly_story_metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="same_elo_cost" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="frontier_only" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="weekly_story_metrics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="same_elo_cost" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NOTES" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E797"/>
+  <dimension ref="A1:E803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rows=793 cols=5</t>
+          <t>rows=799 cols=5</t>
         </is>
       </c>
     </row>
@@ -18696,6 +18696,144 @@
         <v>1384.623689487935</v>
       </c>
       <c r="E797" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D798" t="n">
+        <v>1535.266457716405</v>
+      </c>
+      <c r="E798" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>muse-spark-1.3-max</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D799" t="n">
+        <v>1515.784584495932</v>
+      </c>
+      <c r="E799" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>gemini-3.8-flash-high</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D800" t="n">
+        <v>1513.973595932706</v>
+      </c>
+      <c r="E800" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Z.AI</t>
+        </is>
+      </c>
+      <c r="D801" t="n">
+        <v>1508.267203021079</v>
+      </c>
+      <c r="E801" t="n">
+        <v>0.2375</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>qwen3.5-flash</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
+      <c r="D802" t="n">
+        <v>1413.121390526185</v>
+      </c>
+      <c r="E802" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>glm-4.7-flash</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Z.AI</t>
+        </is>
+      </c>
+      <c r="D803" t="n">
+        <v>1384.888774175552</v>
+      </c>
+      <c r="E803" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18710,7 +18848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18723,7 +18861,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rows=116 cols=7</t>
+          <t>rows=117 cols=7</t>
         </is>
       </c>
     </row>
@@ -21893,6 +22031,33 @@
         <v>1535.487055897384</v>
       </c>
       <c r="G120" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>6</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1535.266457716405</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1535.266457716405</v>
+      </c>
+      <c r="G121" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21907,7 +22072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F507"/>
+  <dimension ref="A1:F513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21920,7 +22085,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rows=503 cols=6</t>
+          <t>rows=509 cols=6</t>
         </is>
       </c>
     </row>
@@ -24975,27 +25140,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1277.627008340256</v>
+        <v>1267.483727997796</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>15</v>
+        <v>0.1275</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>gpt-4-turbo-2024-04-09</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
     </row>
     <row r="122">
@@ -25009,13 +25174,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>15</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>gpt-4-turbo-2024-04-09</t>
+        </is>
+      </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -25029,7 +25200,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -25049,7 +25220,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -25069,7 +25240,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -25089,19 +25260,13 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>gpt-4o-2024-05-13</t>
-        </is>
-      </c>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -25115,7 +25280,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -25141,7 +25306,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -25167,7 +25332,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -25193,7 +25358,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -25219,7 +25384,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -25245,19 +25410,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>claude-3-5-sonnet-20240620</t>
+          <t>gpt-4o-2024-05-13</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -25271,7 +25436,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -25297,7 +25462,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -25323,7 +25488,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -25349,7 +25514,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -25375,19 +25540,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.2624999999999999</v>
+        <v>6</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>gpt-4o-mini-2024-07-18</t>
+          <t>claude-3-5-sonnet-20240620</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -25401,7 +25566,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -25427,7 +25592,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -25453,7 +25618,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -25465,7 +25630,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -25479,7 +25644,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -25505,7 +25670,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -25531,7 +25696,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -25543,7 +25708,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
@@ -25557,7 +25722,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -25569,7 +25734,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -25583,7 +25748,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -25609,7 +25774,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -25621,7 +25786,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
@@ -25635,7 +25800,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -25661,7 +25826,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -25687,7 +25852,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -25699,7 +25864,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
@@ -25713,7 +25878,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -25739,7 +25904,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -25765,7 +25930,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -25791,7 +25956,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -25817,7 +25982,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -25843,7 +26008,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -25869,7 +26034,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -25895,7 +26060,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -25907,7 +26072,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
@@ -25921,7 +26086,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -25947,7 +26112,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -25973,7 +26138,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -25985,7 +26150,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161">
@@ -25999,7 +26164,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -26025,19 +26190,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.175</v>
+        <v>0.2624999999999999</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163">
@@ -26051,7 +26216,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -26077,7 +26242,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -26089,7 +26254,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165">
@@ -26103,7 +26268,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -26129,7 +26294,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -26155,7 +26320,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -26181,7 +26346,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -26193,7 +26358,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169">
@@ -26207,7 +26372,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -26219,7 +26384,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="170">
@@ -26233,7 +26398,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -26259,7 +26424,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -26271,7 +26436,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172">
@@ -26285,7 +26450,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -26297,7 +26462,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173">
@@ -26311,7 +26476,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -26337,7 +26502,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -26349,7 +26514,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175">
@@ -26363,7 +26528,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -26375,7 +26540,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176">
@@ -26389,7 +26554,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -26401,7 +26566,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="177">
@@ -26415,7 +26580,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -26427,7 +26592,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="178">
@@ -26441,7 +26606,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -26453,7 +26618,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179">
@@ -26467,7 +26632,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -26479,7 +26644,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="180">
@@ -26493,7 +26658,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -26505,7 +26670,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="181">
@@ -26519,7 +26684,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -26531,7 +26696,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="182">
@@ -26545,7 +26710,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -26557,7 +26722,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="183">
@@ -26571,7 +26736,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -26583,7 +26748,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="184">
@@ -26597,7 +26762,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -26609,7 +26774,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="185">
@@ -26623,7 +26788,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -26635,7 +26800,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="186">
@@ -26649,7 +26814,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -26657,11 +26822,11 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="187">
@@ -26675,7 +26840,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -26701,7 +26866,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -26713,7 +26878,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="189">
@@ -26727,7 +26892,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -26753,7 +26918,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -26765,7 +26930,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="191">
@@ -26779,7 +26944,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -26791,7 +26956,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192">
@@ -26805,7 +26970,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -26817,7 +26982,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="193">
@@ -26831,7 +26996,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -26843,7 +27008,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="194">
@@ -26857,7 +27022,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -26869,7 +27034,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="195">
@@ -26883,7 +27048,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -26909,7 +27074,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -26921,7 +27086,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="197">
@@ -26935,7 +27100,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -26947,7 +27112,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="198">
@@ -26961,7 +27126,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -26973,7 +27138,7 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="199">
@@ -26987,7 +27152,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -26999,7 +27164,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="200">
@@ -27013,7 +27178,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -27039,7 +27204,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -27051,7 +27216,7 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="202">
@@ -27065,7 +27230,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -27077,7 +27242,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="203">
@@ -27091,7 +27256,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -27103,7 +27268,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="204">
@@ -27117,7 +27282,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -27129,7 +27294,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="205">
@@ -27143,7 +27308,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -27169,7 +27334,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -27181,7 +27346,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="207">
@@ -27195,7 +27360,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -27207,7 +27372,7 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="208">
@@ -27221,7 +27386,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -27233,7 +27398,7 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="209">
@@ -27247,7 +27412,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -27273,19 +27438,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="211">
@@ -27299,7 +27464,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -27311,7 +27476,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="212">
@@ -27325,7 +27490,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -27337,7 +27502,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="213">
@@ -27351,7 +27516,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -27377,7 +27542,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -27389,7 +27554,7 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="215">
@@ -27403,7 +27568,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -27429,7 +27594,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -27441,7 +27606,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="217">
@@ -27455,7 +27620,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -27467,7 +27632,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="218">
@@ -27481,7 +27646,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -27493,7 +27658,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="219">
@@ -27507,7 +27672,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -27519,7 +27684,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="220">
@@ -27533,7 +27698,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -27559,7 +27724,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -27571,7 +27736,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="222">
@@ -27585,7 +27750,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -27597,7 +27762,7 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="223">
@@ -27611,7 +27776,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -27623,7 +27788,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="224">
@@ -27637,7 +27802,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -27649,7 +27814,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="225">
@@ -27663,7 +27828,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -27675,7 +27840,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="226">
@@ -27689,11 +27854,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -27701,7 +27866,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="227">
@@ -27715,19 +27880,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.1275</v>
+        <v>0.11</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="228">
@@ -27741,7 +27906,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -27753,7 +27918,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="229">
@@ -27767,7 +27932,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -27779,7 +27944,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="230">
@@ -27793,7 +27958,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -27805,7 +27970,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="231">
@@ -27819,7 +27984,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -27831,7 +27996,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="232">
@@ -27845,7 +28010,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -27857,7 +28022,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="233">
@@ -27871,7 +28036,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -27883,7 +28048,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="234">
@@ -27897,7 +28062,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -27909,7 +28074,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="235">
@@ -27923,71 +28088,71 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.11875</v>
+        <v>0.1275</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1300.50868831193</v>
+        <v>1277.627008340256</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>6</v>
+        <v>0.11875</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>claude-3-5-sonnet-20240620</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1300.50868831193</v>
+        <v>1277.627008340256</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>6</v>
+        <v>0.1275</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>claude-3-5-sonnet-20240620</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
     </row>
     <row r="238">
@@ -28001,7 +28166,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -28027,7 +28192,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -28053,13 +28218,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>6</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>claude-3-5-sonnet-20240620</t>
+        </is>
+      </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -28073,13 +28244,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>6</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>claude-3-5-sonnet-20240620</t>
+        </is>
+      </c>
       <c r="F241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -28093,7 +28270,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -28113,19 +28290,13 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>chatgpt-4o-latest</t>
-        </is>
-      </c>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -28139,19 +28310,13 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>chatgpt-4o-latest</t>
-        </is>
-      </c>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -28165,7 +28330,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -28191,13 +28356,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>chatgpt-4o-latest</t>
+        </is>
+      </c>
       <c r="F246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -28211,15 +28382,15 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1.925</v>
+        <v>4.375</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>o1-mini</t>
+          <t>chatgpt-4o-latest</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -28237,19 +28408,13 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>1.925</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>o1-mini</t>
-        </is>
-      </c>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -28263,7 +28428,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -28289,7 +28454,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -28315,7 +28480,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -28341,7 +28506,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -28353,7 +28518,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -28367,7 +28532,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -28379,7 +28544,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -28393,7 +28558,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -28419,7 +28584,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -28445,7 +28610,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -28471,7 +28636,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -28497,7 +28662,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -28523,7 +28688,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -28549,7 +28714,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -28561,7 +28726,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
@@ -28575,7 +28740,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -28587,7 +28752,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -28601,7 +28766,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -28627,7 +28792,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -28653,7 +28818,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -28679,19 +28844,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>0.175</v>
+        <v>1.925</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>o1-mini</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266">
@@ -28705,19 +28870,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.175</v>
+        <v>1.925</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>o1-mini</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
@@ -28731,7 +28896,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="D267" t="n">
@@ -28743,7 +28908,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268">
@@ -28757,7 +28922,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="D268" t="n">
@@ -28769,7 +28934,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269">
@@ -28783,7 +28948,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -28809,7 +28974,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -28835,7 +29000,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -28847,7 +29012,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="272">
@@ -28861,7 +29026,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -28873,7 +29038,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273">
@@ -28887,7 +29052,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -28899,7 +29064,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="274">
@@ -28913,7 +29078,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -28939,7 +29104,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -28951,7 +29116,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="276">
@@ -28965,7 +29130,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -28977,7 +29142,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="277">
@@ -28991,7 +29156,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -29017,7 +29182,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -29029,7 +29194,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="279">
@@ -29043,7 +29208,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -29055,7 +29220,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="280">
@@ -29069,7 +29234,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -29081,7 +29246,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="281">
@@ -29095,7 +29260,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -29107,7 +29272,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="282">
@@ -29121,7 +29286,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -29133,7 +29298,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="283">
@@ -29147,7 +29312,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -29159,7 +29324,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="284">
@@ -29173,7 +29338,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -29199,7 +29364,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -29211,7 +29376,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="286">
@@ -29225,7 +29390,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -29237,7 +29402,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="287">
@@ -29251,7 +29416,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -29277,7 +29442,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -29289,7 +29454,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="289">
@@ -29303,7 +29468,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -29311,11 +29476,11 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="290">
@@ -29329,7 +29494,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -29337,11 +29502,11 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F290" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="291">
@@ -29355,7 +29520,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -29367,7 +29532,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="292">
@@ -29381,7 +29546,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -29393,7 +29558,7 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="293">
@@ -29407,7 +29572,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -29433,7 +29598,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -29445,7 +29610,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="295">
@@ -29459,7 +29624,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -29471,7 +29636,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="296">
@@ -29485,7 +29650,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -29497,7 +29662,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="297">
@@ -29511,7 +29676,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -29523,7 +29688,7 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="298">
@@ -29537,7 +29702,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -29549,7 +29714,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="299">
@@ -29563,7 +29728,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -29575,7 +29740,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="300">
@@ -29589,7 +29754,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -29601,7 +29766,7 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="301">
@@ -29615,7 +29780,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -29627,7 +29792,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="302">
@@ -29641,7 +29806,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -29653,7 +29818,7 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="303">
@@ -29667,7 +29832,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -29679,7 +29844,7 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="304">
@@ -29693,7 +29858,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -29705,7 +29870,7 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="305">
@@ -29719,7 +29884,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -29731,7 +29896,7 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="306">
@@ -29745,7 +29910,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -29757,7 +29922,7 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="307">
@@ -29771,7 +29936,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -29783,7 +29948,7 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="308">
@@ -29797,7 +29962,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -29809,7 +29974,7 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="309">
@@ -29823,7 +29988,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -29835,7 +30000,7 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="310">
@@ -29849,7 +30014,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D310" t="n">
@@ -29861,7 +30026,7 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="311">
@@ -29875,7 +30040,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D311" t="n">
@@ -29887,7 +30052,7 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="312">
@@ -29901,7 +30066,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D312" t="n">
@@ -29913,7 +30078,7 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="313">
@@ -29927,19 +30092,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="314">
@@ -29953,19 +30118,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="315">
@@ -29979,7 +30144,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D315" t="n">
@@ -29991,7 +30156,7 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="316">
@@ -30005,7 +30170,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D316" t="n">
@@ -30017,7 +30182,7 @@
         </is>
       </c>
       <c r="F316" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="317">
@@ -30031,7 +30196,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D317" t="n">
@@ -30043,7 +30208,7 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="318">
@@ -30057,7 +30222,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -30069,7 +30234,7 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="319">
@@ -30083,7 +30248,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D319" t="n">
@@ -30095,7 +30260,7 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="320">
@@ -30109,7 +30274,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -30121,7 +30286,7 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="321">
@@ -30135,7 +30300,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D321" t="n">
@@ -30147,7 +30312,7 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="322">
@@ -30161,7 +30326,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D322" t="n">
@@ -30173,7 +30338,7 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="323">
@@ -30187,7 +30352,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -30199,7 +30364,7 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="324">
@@ -30213,7 +30378,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D324" t="n">
@@ -30225,7 +30390,7 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="325">
@@ -30239,7 +30404,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D325" t="n">
@@ -30251,7 +30416,7 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="326">
@@ -30265,7 +30430,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D326" t="n">
@@ -30277,7 +30442,7 @@
         </is>
       </c>
       <c r="F326" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="327">
@@ -30291,7 +30456,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D327" t="n">
@@ -30317,7 +30482,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -30329,7 +30494,7 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="329">
@@ -30343,11 +30508,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -30355,7 +30520,7 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="330">
@@ -30369,19 +30534,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>0.1275</v>
+        <v>0.09</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="331">
@@ -30395,19 +30560,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>0.1275</v>
+        <v>0.11</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F331" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="332">
@@ -30421,7 +30586,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -30433,7 +30598,7 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="333">
@@ -30447,7 +30612,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -30459,7 +30624,7 @@
         </is>
       </c>
       <c r="F333" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="334">
@@ -30473,7 +30638,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -30485,7 +30650,7 @@
         </is>
       </c>
       <c r="F334" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="335">
@@ -30499,7 +30664,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -30511,7 +30676,7 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="336">
@@ -30525,7 +30690,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -30537,7 +30702,7 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="337">
@@ -30551,7 +30716,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -30563,7 +30728,7 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="338">
@@ -30577,97 +30742,97 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>0.11875</v>
+        <v>0.1275</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F338" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>1359.023816493652</v>
+        <v>1300.50868831193</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1.925</v>
+        <v>0.1275</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>o1-mini</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F339" t="n">
-        <v>1</v>
+        <v>121</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>1359.023816493652</v>
+        <v>1300.50868831193</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>26.25</v>
+        <v>0.11875</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>o1-2024-12-17</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>1359.023816493652</v>
+        <v>1300.50868831193</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>26.25</v>
+        <v>0.1275</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>o1-2024-12-17</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="342">
@@ -30681,15 +30846,15 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>26.25</v>
+        <v>1.925</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>o1-2024-12-17</t>
+          <t>o1-mini</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -30707,7 +30872,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D343" t="n">
@@ -30733,7 +30898,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="D344" t="n">
@@ -30759,7 +30924,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="D345" t="n">
@@ -30785,19 +30950,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>1.925</v>
+        <v>26.25</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>o3-mini-high</t>
+          <t>o1-2024-12-17</t>
         </is>
       </c>
       <c r="F346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -30811,19 +30976,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1.925</v>
+        <v>26.25</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>o3-mini-high</t>
+          <t>o1-2024-12-17</t>
         </is>
       </c>
       <c r="F347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
@@ -30837,19 +31002,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1.925</v>
+        <v>26.25</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>o3-mini-high</t>
+          <t>o1-2024-12-17</t>
         </is>
       </c>
       <c r="F348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -30863,7 +31028,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -30875,7 +31040,7 @@
         </is>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350">
@@ -30889,7 +31054,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -30901,7 +31066,7 @@
         </is>
       </c>
       <c r="F350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
@@ -30915,7 +31080,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -30941,7 +31106,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -30953,7 +31118,7 @@
         </is>
       </c>
       <c r="F352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -30967,7 +31132,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -30979,7 +31144,7 @@
         </is>
       </c>
       <c r="F353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -30993,7 +31158,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -31001,11 +31166,11 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>o4-mini-2025-04-16</t>
+          <t>o3-mini-high</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="355">
@@ -31019,19 +31184,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.925</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>gpt-4.1-mini-2025-04-14</t>
+          <t>o3-mini-high</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="356">
@@ -31045,7 +31210,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -31053,11 +31218,11 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>o4-mini-2025-04-16</t>
+          <t>o3-mini-high</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357">
@@ -31071,19 +31236,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.925</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>gpt-4.1-mini-2025-04-14</t>
+          <t>o4-mini-2025-04-16</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="358">
@@ -31097,7 +31262,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -31109,7 +31274,7 @@
         </is>
       </c>
       <c r="F358" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="359">
@@ -31123,19 +31288,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0.175</v>
+        <v>1.925</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>o4-mini-2025-04-16</t>
         </is>
       </c>
       <c r="F359" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360">
@@ -31149,19 +31314,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.175</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>gpt-4.1-mini-2025-04-14</t>
         </is>
       </c>
       <c r="F360" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="361">
@@ -31175,19 +31340,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0.175</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>gpt-4.1-mini-2025-04-14</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="362">
@@ -31201,7 +31366,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="D362" t="n">
@@ -31213,7 +31378,7 @@
         </is>
       </c>
       <c r="F362" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="363">
@@ -31227,7 +31392,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="D363" t="n">
@@ -31239,7 +31404,7 @@
         </is>
       </c>
       <c r="F363" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="364">
@@ -31253,7 +31418,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -31265,7 +31430,7 @@
         </is>
       </c>
       <c r="F364" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="365">
@@ -31279,7 +31444,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -31291,7 +31456,7 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="366">
@@ -31305,7 +31470,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -31317,7 +31482,7 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="367">
@@ -31331,7 +31496,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -31357,7 +31522,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -31365,11 +31530,11 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F368" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="369">
@@ -31383,7 +31548,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -31391,11 +31556,11 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F369" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="370">
@@ -31409,7 +31574,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -31417,11 +31582,11 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F370" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="371">
@@ -31435,7 +31600,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -31447,7 +31612,7 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="372">
@@ -31461,7 +31626,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -31473,7 +31638,7 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="373">
@@ -31487,7 +31652,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -31499,7 +31664,7 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="374">
@@ -31513,7 +31678,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -31525,7 +31690,7 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="375">
@@ -31539,7 +31704,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -31551,7 +31716,7 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="376">
@@ -31565,7 +31730,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -31577,7 +31742,7 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="377">
@@ -31591,7 +31756,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -31603,7 +31768,7 @@
         </is>
       </c>
       <c r="F377" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="378">
@@ -31617,7 +31782,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -31629,7 +31794,7 @@
         </is>
       </c>
       <c r="F378" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="379">
@@ -31643,7 +31808,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -31655,7 +31820,7 @@
         </is>
       </c>
       <c r="F379" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="380">
@@ -31669,7 +31834,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -31681,7 +31846,7 @@
         </is>
       </c>
       <c r="F380" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="381">
@@ -31695,7 +31860,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D381" t="n">
@@ -31707,7 +31872,7 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="382">
@@ -31721,7 +31886,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D382" t="n">
@@ -31733,7 +31898,7 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="383">
@@ -31747,7 +31912,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -31759,7 +31924,7 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="384">
@@ -31773,7 +31938,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D384" t="n">
@@ -31785,7 +31950,7 @@
         </is>
       </c>
       <c r="F384" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="385">
@@ -31799,7 +31964,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -31811,7 +31976,7 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="386">
@@ -31825,7 +31990,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -31837,7 +32002,7 @@
         </is>
       </c>
       <c r="F386" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="387">
@@ -31851,7 +32016,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -31863,7 +32028,7 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="388">
@@ -31877,7 +32042,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -31889,7 +32054,7 @@
         </is>
       </c>
       <c r="F388" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="389">
@@ -31903,7 +32068,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D389" t="n">
@@ -31915,7 +32080,7 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="390">
@@ -31929,7 +32094,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -31941,7 +32106,7 @@
         </is>
       </c>
       <c r="F390" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="391">
@@ -31955,7 +32120,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -31967,7 +32132,7 @@
         </is>
       </c>
       <c r="F391" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="392">
@@ -31981,19 +32146,19 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F392" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="393">
@@ -32007,19 +32172,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F393" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="394">
@@ -32033,19 +32198,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F394" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="395">
@@ -32059,7 +32224,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D395" t="n">
@@ -32071,7 +32236,7 @@
         </is>
       </c>
       <c r="F395" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="396">
@@ -32085,7 +32250,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -32097,7 +32262,7 @@
         </is>
       </c>
       <c r="F396" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="397">
@@ -32111,7 +32276,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -32123,7 +32288,7 @@
         </is>
       </c>
       <c r="F397" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="398">
@@ -32137,7 +32302,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -32149,7 +32314,7 @@
         </is>
       </c>
       <c r="F398" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="399">
@@ -32163,7 +32328,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -32175,7 +32340,7 @@
         </is>
       </c>
       <c r="F399" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="400">
@@ -32189,7 +32354,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -32201,7 +32366,7 @@
         </is>
       </c>
       <c r="F400" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="401">
@@ -32215,7 +32380,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -32227,7 +32392,7 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="402">
@@ -32241,7 +32406,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -32253,7 +32418,7 @@
         </is>
       </c>
       <c r="F402" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="403">
@@ -32267,7 +32432,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -32279,7 +32444,7 @@
         </is>
       </c>
       <c r="F403" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="404">
@@ -32293,7 +32458,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -32305,7 +32470,7 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="405">
@@ -32319,7 +32484,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D405" t="n">
@@ -32331,7 +32496,7 @@
         </is>
       </c>
       <c r="F405" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="406">
@@ -32345,7 +32510,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D406" t="n">
@@ -32357,7 +32522,7 @@
         </is>
       </c>
       <c r="F406" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="407">
@@ -32371,7 +32536,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D407" t="n">
@@ -32383,7 +32548,7 @@
         </is>
       </c>
       <c r="F407" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="408">
@@ -32397,11 +32562,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -32409,7 +32574,7 @@
         </is>
       </c>
       <c r="F408" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="409">
@@ -32423,11 +32588,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -32435,7 +32600,7 @@
         </is>
       </c>
       <c r="F409" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="410">
@@ -32449,11 +32614,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -32461,7 +32626,7 @@
         </is>
       </c>
       <c r="F410" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="411">
@@ -32475,11 +32640,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -32487,7 +32652,7 @@
         </is>
       </c>
       <c r="F411" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="412">
@@ -32501,7 +32666,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D412" t="n">
@@ -32513,7 +32678,7 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="413">
@@ -32527,7 +32692,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D413" t="n">
@@ -32539,7 +32704,7 @@
         </is>
       </c>
       <c r="F413" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="414">
@@ -32553,7 +32718,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D414" t="n">
@@ -32565,7 +32730,7 @@
         </is>
       </c>
       <c r="F414" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="415">
@@ -32579,7 +32744,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D415" t="n">
@@ -32591,7 +32756,7 @@
         </is>
       </c>
       <c r="F415" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
     <row r="416">
@@ -32605,7 +32770,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D416" t="n">
@@ -32617,7 +32782,7 @@
         </is>
       </c>
       <c r="F416" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="417">
@@ -32631,105 +32796,123 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>0.11875</v>
+        <v>0.15</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F417" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>1491.030286935986</v>
+        <v>1359.023816493652</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>3.4375</v>
+        <v>0.15</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>gemini-2.5-pro</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F418" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>1491.030286935986</v>
+        <v>1359.023816493652</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr"/>
-      <c r="E419" t="inlineStr"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>mistral-small-2506</t>
+        </is>
+      </c>
       <c r="F419" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>1491.030286935986</v>
+        <v>1359.023816493652</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>glm-5.3-flash</t>
+        </is>
+      </c>
       <c r="F420" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>1491.030286935986</v>
+        <v>1359.023816493652</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="inlineStr"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>mistral-small-2506</t>
+        </is>
+      </c>
       <c r="F421" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
     </row>
     <row r="422">
@@ -32743,13 +32926,19 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
-      <c r="E422" t="inlineStr"/>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>3.4375</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>gemini-2.5-pro</t>
+        </is>
+      </c>
       <c r="F422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -32763,7 +32952,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -32783,7 +32972,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -32803,7 +32992,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -32823,7 +33012,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -32843,7 +33032,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -32863,7 +33052,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -32883,7 +33072,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -32903,19 +33092,13 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="D430" t="n">
-        <v>6</v>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
-        </is>
-      </c>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr"/>
       <c r="F430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -32929,19 +33112,13 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="D431" t="n">
-        <v>6</v>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
-        </is>
-      </c>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr"/>
       <c r="F431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -32955,19 +33132,13 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="D432" t="n">
-        <v>6</v>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
-        </is>
-      </c>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr"/>
       <c r="F432" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -32981,19 +33152,13 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="D433" t="n">
-        <v>6</v>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
-        </is>
-      </c>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr"/>
       <c r="F433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -33007,7 +33172,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -33033,7 +33198,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -33045,7 +33210,7 @@
         </is>
       </c>
       <c r="F435" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -33059,7 +33224,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D436" t="n">
@@ -33071,7 +33236,7 @@
         </is>
       </c>
       <c r="F436" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -33085,7 +33250,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D437" t="n">
@@ -33097,7 +33262,7 @@
         </is>
       </c>
       <c r="F437" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -33111,7 +33276,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D438" t="n">
@@ -33123,7 +33288,7 @@
         </is>
       </c>
       <c r="F438" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -33137,7 +33302,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D439" t="n">
@@ -33163,7 +33328,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D440" t="n">
@@ -33189,7 +33354,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D441" t="n">
@@ -33215,19 +33380,19 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-thinking-32k</t>
+          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
         </is>
       </c>
       <c r="F442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="443">
@@ -33241,19 +33406,19 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-thinking-32k</t>
+          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
         </is>
       </c>
       <c r="F443" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="444">
@@ -33267,19 +33432,19 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
         </is>
       </c>
       <c r="F444" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="445">
@@ -33293,19 +33458,19 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
         </is>
       </c>
       <c r="F445" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="446">
@@ -33319,19 +33484,19 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>claude-opus-4-5-20251101-thinking-32k</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="447">
@@ -33345,19 +33510,19 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>claude-opus-4-5-20251101-thinking-32k</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="448">
@@ -33371,19 +33536,19 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="449">
@@ -33397,19 +33562,19 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="450">
@@ -33423,7 +33588,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -33435,7 +33600,7 @@
         </is>
       </c>
       <c r="F450" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="451">
@@ -33449,7 +33614,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -33461,7 +33626,7 @@
         </is>
       </c>
       <c r="F451" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="452">
@@ -33475,7 +33640,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -33501,7 +33666,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D453" t="n">
@@ -33527,7 +33692,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -33539,7 +33704,7 @@
         </is>
       </c>
       <c r="F454" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="455">
@@ -33553,7 +33718,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D455" t="n">
@@ -33565,7 +33730,7 @@
         </is>
       </c>
       <c r="F455" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="456">
@@ -33579,7 +33744,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D456" t="n">
@@ -33591,7 +33756,7 @@
         </is>
       </c>
       <c r="F456" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="457">
@@ -33605,7 +33770,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D457" t="n">
@@ -33617,7 +33782,7 @@
         </is>
       </c>
       <c r="F457" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="458">
@@ -33631,19 +33796,19 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>5.625</v>
+        <v>4.5</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>gpt-5.4-high</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F458" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="459">
@@ -33657,19 +33822,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>3.375</v>
+        <v>4.5</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F459" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="460">
@@ -33683,19 +33848,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>qwen3.7-max-preview</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F460" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="461">
@@ -33709,19 +33874,19 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>3.375</v>
+        <v>4.5</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F461" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="462">
@@ -33735,19 +33900,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>3.75</v>
+        <v>5.625</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>qwen3.7-max-preview</t>
+          <t>gpt-5.4-high</t>
         </is>
       </c>
       <c r="F462" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="463">
@@ -33761,7 +33926,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D463" t="n">
@@ -33773,7 +33938,7 @@
         </is>
       </c>
       <c r="F463" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="464">
@@ -33787,19 +33952,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>qwen3.7-max-preview</t>
         </is>
       </c>
       <c r="F464" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="465">
@@ -33813,19 +33978,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>2.15</v>
+        <v>3.375</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>gemini-3.5-flash</t>
         </is>
       </c>
       <c r="F465" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="466">
@@ -33839,19 +34004,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>qwen3.7-max-preview</t>
         </is>
       </c>
       <c r="F466" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="467">
@@ -33865,19 +34030,19 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>2.15</v>
+        <v>3.375</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>gemini-3.5-flash</t>
         </is>
       </c>
       <c r="F467" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="468">
@@ -33891,7 +34056,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -33903,7 +34068,7 @@
         </is>
       </c>
       <c r="F468" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="469">
@@ -33917,19 +34082,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>muse-spark-1.1</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="F469" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="470">
@@ -33943,19 +34108,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>muse-spark-1.1</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="F470" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="471">
@@ -33969,19 +34134,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash-high</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="F471" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="472">
@@ -33995,19 +34160,19 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash-high</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="F472" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="473">
@@ -34021,137 +34186,149 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>0.11875</v>
+        <v>2</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>muse-spark-1.1</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-thinking-32k</t>
+          <t>muse-spark-1.1</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-thinking-32k</t>
+          <t>gemini-3.7-flash-high</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr"/>
-      <c r="E476" t="inlineStr"/>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>gemini-3.7-flash-high</t>
+        </is>
+      </c>
       <c r="F476" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr"/>
-      <c r="E477" t="inlineStr"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>glm-5.3-flash</t>
+        </is>
+      </c>
       <c r="F477" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>10</v>
+        <v>0.2375</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="479">
@@ -34165,7 +34342,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D479" t="n">
@@ -34173,11 +34350,11 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-opus-4-5-20251101-thinking-32k</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -34191,7 +34368,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D480" t="n">
@@ -34199,11 +34376,11 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-opus-4-5-20251101-thinking-32k</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481">
@@ -34217,19 +34394,13 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="D481" t="n">
-        <v>10</v>
-      </c>
-      <c r="E481" t="inlineStr">
-        <is>
-          <t>claude-opus-4-6-thinking</t>
-        </is>
-      </c>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
+      <c r="E481" t="inlineStr"/>
       <c r="F481" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482">
@@ -34243,19 +34414,13 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="D482" t="n">
-        <v>5.625</v>
-      </c>
-      <c r="E482" t="inlineStr">
-        <is>
-          <t>gpt-5.4-high</t>
-        </is>
-      </c>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" t="inlineStr"/>
       <c r="F482" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -34269,7 +34434,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -34295,7 +34460,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -34321,7 +34486,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D485" t="n">
@@ -34347,7 +34512,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -34373,19 +34538,19 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>10</v>
+        <v>5.625</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>gpt-5.4-high</t>
         </is>
       </c>
       <c r="F487" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -34399,7 +34564,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D488" t="n">
@@ -34407,11 +34572,11 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F488" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="489">
@@ -34425,7 +34590,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D489" t="n">
@@ -34437,7 +34602,7 @@
         </is>
       </c>
       <c r="F489" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="490">
@@ -34451,7 +34616,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -34459,11 +34624,11 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F490" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="491">
@@ -34477,7 +34642,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D491" t="n">
@@ -34485,11 +34650,11 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F491" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="492">
@@ -34503,7 +34668,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D492" t="n">
@@ -34511,11 +34676,11 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="493">
@@ -34529,7 +34694,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D493" t="n">
@@ -34537,11 +34702,11 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="494">
@@ -34555,7 +34720,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D494" t="n">
@@ -34563,7 +34728,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F494" t="n">
@@ -34581,7 +34746,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D495" t="n">
@@ -34593,7 +34758,7 @@
         </is>
       </c>
       <c r="F495" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="496">
@@ -34607,7 +34772,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -34633,7 +34798,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -34645,7 +34810,7 @@
         </is>
       </c>
       <c r="F497" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="498">
@@ -34659,7 +34824,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -34667,11 +34832,11 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -34685,7 +34850,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D499" t="n">
@@ -34697,7 +34862,7 @@
         </is>
       </c>
       <c r="F499" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="500">
@@ -34711,7 +34876,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -34723,7 +34888,7 @@
         </is>
       </c>
       <c r="F500" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -34737,7 +34902,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -34763,7 +34928,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D502" t="n">
@@ -34775,7 +34940,7 @@
         </is>
       </c>
       <c r="F502" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="503">
@@ -34789,7 +34954,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D503" t="n">
@@ -34801,7 +34966,7 @@
         </is>
       </c>
       <c r="F503" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="504">
@@ -34815,7 +34980,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D504" t="n">
@@ -34823,11 +34988,11 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F504" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="505">
@@ -34841,7 +35006,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D505" t="n">
@@ -34849,11 +35014,11 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F505" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506">
@@ -34867,7 +35032,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -34875,11 +35040,11 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F506" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="507">
@@ -34893,7 +35058,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -34901,10 +35066,166 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="F507" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>10</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6</t>
+        </is>
+      </c>
+      <c r="F508" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>10</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-thinking</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>10</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
           <t>claude-opus-4-6-high</t>
         </is>
       </c>
-      <c r="F507" t="n">
+      <c r="F510" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>10</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="F511" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>10</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="F512" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>10</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="F513" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34925,7 +35246,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Pareto coding frontier export — 2026-09-11</t>
+          <t>Pareto coding frontier export — 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -34935,35 +35256,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Primary story: Arena Text *coding* Elo vs blended $/MTok over time</t>
+          <t>Primary story: Arena Text/coding score vs blended $/MTok over time</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NOT overall Text Elo — coding category only</t>
+          <t>NOT overall Text or WebDev — coding category only</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Panel weeks: 2024-04-01 → 2026-08-31 (116 weeks)</t>
+          <t>Panel weeks: 2024-04-01 → 2026-09-07 (117 weeks)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Match rate: 196/418 (46.9%)</t>
+          <t>Match rate: 198/420 (47.1%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Astra / DeepSeek V4.1 Flash omitted — no Text-coding Arena Elo yet (see Code Arena tip / AA tip)</t>
+          <t>GPT-6 Astra Max rated on Text/coding from week 2026-09-07; DeepSeek V4.1 Flash is rated on WebDev only</t>
         </is>
       </c>
     </row>

--- a/data/export/coding/pareto_coding_frontier_story_data.xlsx
+++ b/data/export/coding/pareto_coding_frontier_story_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E803"/>
+  <dimension ref="A1:E811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,7 +429,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rows=799 cols=5</t>
+          <t>rows=807 cols=5</t>
         </is>
       </c>
     </row>
@@ -18834,6 +18834,190 @@
         <v>1384.888774175552</v>
       </c>
       <c r="E803" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>claude-opus-5.5-high</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D804" t="n">
+        <v>1545.204286365697</v>
+      </c>
+      <c r="E804" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>muse-spark-1.3-max</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="D805" t="n">
+        <v>1515.779707460659</v>
+      </c>
+      <c r="E805" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>gemini-3.8-flash-high</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="D806" t="n">
+        <v>1511.513487736478</v>
+      </c>
+      <c r="E806" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>deepseek-v4.1-flash-max</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="D807" t="n">
+        <v>1511.262994857263</v>
+      </c>
+      <c r="E807" t="n">
+        <v>0.5249999999999999</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Z.AI</t>
+        </is>
+      </c>
+      <c r="D808" t="n">
+        <v>1506.049253648251</v>
+      </c>
+      <c r="E808" t="n">
+        <v>0.2375</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>gpt-6-luna-max</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="D809" t="n">
+        <v>1447.942652095372</v>
+      </c>
+      <c r="E809" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>qwen3.5-flash</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
+      <c r="D810" t="n">
+        <v>1412.19003151889</v>
+      </c>
+      <c r="E810" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>glm-4.7-flash</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Z.AI</t>
+        </is>
+      </c>
+      <c r="D811" t="n">
+        <v>1382.927722303048</v>
+      </c>
+      <c r="E811" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18848,7 +19032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18861,7 +19045,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rows=117 cols=7</t>
+          <t>rows=118 cols=7</t>
         </is>
       </c>
     </row>
@@ -22059,6 +22243,33 @@
       </c>
       <c r="G121" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>8</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1545.204286365697</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>claude-opus-5.5-high</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1545.204286365697</v>
+      </c>
+      <c r="G122" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -22072,7 +22283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F513"/>
+  <dimension ref="A1:F519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22085,7 +22296,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rows=509 cols=6</t>
+          <t>rows=515 cols=6</t>
         </is>
       </c>
     </row>
@@ -25166,27 +25377,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1277.627008340256</v>
+        <v>1267.483727997796</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>15</v>
+        <v>0.1275</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>gpt-4-turbo-2024-04-09</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>145</v>
       </c>
     </row>
     <row r="123">
@@ -25200,13 +25411,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>15</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>gpt-4-turbo-2024-04-09</t>
+        </is>
+      </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -25220,7 +25437,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -25240,7 +25457,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -25260,7 +25477,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -25280,19 +25497,13 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>gpt-4o-2024-05-13</t>
-        </is>
-      </c>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -25306,7 +25517,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -25332,7 +25543,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -25358,7 +25569,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -25384,7 +25595,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -25410,7 +25621,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -25436,19 +25647,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>claude-3-5-sonnet-20240620</t>
+          <t>gpt-4o-2024-05-13</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -25462,7 +25673,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -25488,7 +25699,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -25514,7 +25725,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -25540,7 +25751,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -25566,19 +25777,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.2624999999999999</v>
+        <v>6</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>gpt-4o-mini-2024-07-18</t>
+          <t>claude-3-5-sonnet-20240620</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -25592,7 +25803,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -25618,7 +25829,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -25644,7 +25855,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -25656,7 +25867,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -25670,7 +25881,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -25696,7 +25907,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -25722,7 +25933,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -25734,7 +25945,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
@@ -25748,7 +25959,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -25760,7 +25971,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -25774,7 +25985,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -25800,7 +26011,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -25812,7 +26023,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148">
@@ -25826,7 +26037,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -25852,7 +26063,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -25878,7 +26089,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -25890,7 +26101,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -25904,7 +26115,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -25930,7 +26141,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -25956,7 +26167,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -25982,7 +26193,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -26008,7 +26219,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -26034,7 +26245,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -26060,7 +26271,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -26086,7 +26297,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -26098,7 +26309,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
@@ -26112,7 +26323,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -26138,7 +26349,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -26164,7 +26375,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -26176,7 +26387,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162">
@@ -26190,7 +26401,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -26216,19 +26427,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.175</v>
+        <v>0.2624999999999999</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164">
@@ -26242,7 +26453,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -26268,7 +26479,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -26280,7 +26491,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166">
@@ -26294,7 +26505,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -26320,7 +26531,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -26346,7 +26557,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -26372,7 +26583,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -26384,7 +26595,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
@@ -26398,7 +26609,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -26410,7 +26621,7 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171">
@@ -26424,7 +26635,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -26450,7 +26661,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -26462,7 +26673,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173">
@@ -26476,7 +26687,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -26488,7 +26699,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174">
@@ -26502,7 +26713,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -26528,7 +26739,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -26540,7 +26751,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176">
@@ -26554,7 +26765,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -26566,7 +26777,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177">
@@ -26580,7 +26791,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -26592,7 +26803,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178">
@@ -26606,7 +26817,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -26618,7 +26829,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="179">
@@ -26632,7 +26843,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -26644,7 +26855,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="180">
@@ -26658,7 +26869,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -26670,7 +26881,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="181">
@@ -26684,7 +26895,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -26696,7 +26907,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182">
@@ -26710,7 +26921,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -26722,7 +26933,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183">
@@ -26736,7 +26947,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -26748,7 +26959,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184">
@@ -26762,7 +26973,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -26774,7 +26985,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="185">
@@ -26788,7 +26999,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -26800,7 +27011,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="186">
@@ -26814,7 +27025,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -26826,7 +27037,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="187">
@@ -26840,7 +27051,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -26848,11 +27059,11 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="188">
@@ -26866,7 +27077,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -26892,7 +27103,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -26904,7 +27115,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190">
@@ -26918,7 +27129,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -26944,7 +27155,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -26956,7 +27167,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="192">
@@ -26970,7 +27181,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -26982,7 +27193,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="193">
@@ -26996,7 +27207,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -27008,7 +27219,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="194">
@@ -27022,7 +27233,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -27034,7 +27245,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="195">
@@ -27048,7 +27259,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -27060,7 +27271,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="196">
@@ -27074,7 +27285,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -27100,7 +27311,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -27112,7 +27323,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="198">
@@ -27126,7 +27337,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -27138,7 +27349,7 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="199">
@@ -27152,7 +27363,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -27164,7 +27375,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="200">
@@ -27178,7 +27389,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -27190,7 +27401,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="201">
@@ -27204,7 +27415,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -27230,7 +27441,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -27242,7 +27453,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="203">
@@ -27256,7 +27467,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -27268,7 +27479,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="204">
@@ -27282,7 +27493,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -27294,7 +27505,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="205">
@@ -27308,7 +27519,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -27320,7 +27531,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="206">
@@ -27334,7 +27545,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -27360,7 +27571,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -27372,7 +27583,7 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="208">
@@ -27386,7 +27597,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -27398,7 +27609,7 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="209">
@@ -27412,7 +27623,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -27424,7 +27635,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="210">
@@ -27438,7 +27649,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -27464,19 +27675,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="212">
@@ -27490,7 +27701,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -27502,7 +27713,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="213">
@@ -27516,7 +27727,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -27528,7 +27739,7 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="214">
@@ -27542,7 +27753,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -27568,7 +27779,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -27580,7 +27791,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="216">
@@ -27594,7 +27805,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -27620,7 +27831,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -27632,7 +27843,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="218">
@@ -27646,7 +27857,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -27658,7 +27869,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="219">
@@ -27672,7 +27883,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -27684,7 +27895,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="220">
@@ -27698,7 +27909,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -27710,7 +27921,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="221">
@@ -27724,7 +27935,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -27750,7 +27961,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -27762,7 +27973,7 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="223">
@@ -27776,7 +27987,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -27788,7 +27999,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="224">
@@ -27802,7 +28013,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -27814,7 +28025,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="225">
@@ -27828,7 +28039,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -27840,7 +28051,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="226">
@@ -27854,7 +28065,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -27866,7 +28077,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="227">
@@ -27880,11 +28091,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -27892,7 +28103,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="228">
@@ -27906,19 +28117,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.1275</v>
+        <v>0.11</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="229">
@@ -27932,7 +28143,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -27944,7 +28155,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="230">
@@ -27958,7 +28169,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -27970,7 +28181,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="231">
@@ -27984,7 +28195,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -27996,7 +28207,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="232">
@@ -28010,7 +28221,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -28022,7 +28233,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="233">
@@ -28036,7 +28247,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -28048,7 +28259,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="234">
@@ -28062,7 +28273,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -28074,7 +28285,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="235">
@@ -28088,7 +28299,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -28100,7 +28311,7 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="236">
@@ -28114,19 +28325,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.11875</v>
+        <v>0.1275</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="237">
@@ -28140,71 +28351,71 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.1275</v>
+        <v>0.11875</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1300.50868831193</v>
+        <v>1277.627008340256</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>6</v>
+        <v>0.1275</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>claude-3-5-sonnet-20240620</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1300.50868831193</v>
+        <v>1277.627008340256</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>6</v>
+        <v>0.1275</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>claude-3-5-sonnet-20240620</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
     </row>
     <row r="240">
@@ -28218,7 +28429,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -28244,7 +28455,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -28270,13 +28481,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>6</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>claude-3-5-sonnet-20240620</t>
+        </is>
+      </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -28290,13 +28507,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>6</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>claude-3-5-sonnet-20240620</t>
+        </is>
+      </c>
       <c r="F243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -28310,7 +28533,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -28330,19 +28553,13 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>chatgpt-4o-latest</t>
-        </is>
-      </c>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -28356,19 +28573,13 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>chatgpt-4o-latest</t>
-        </is>
-      </c>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -28382,7 +28593,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -28408,13 +28619,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>chatgpt-4o-latest</t>
+        </is>
+      </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -28428,15 +28645,15 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1.925</v>
+        <v>4.375</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>o1-mini</t>
+          <t>chatgpt-4o-latest</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -28454,19 +28671,13 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>1.925</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>o1-mini</t>
-        </is>
-      </c>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -28480,7 +28691,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -28506,7 +28717,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -28532,7 +28743,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -28558,7 +28769,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -28570,7 +28781,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
@@ -28584,7 +28795,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -28596,7 +28807,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -28610,7 +28821,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -28636,7 +28847,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -28662,7 +28873,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -28688,7 +28899,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -28714,7 +28925,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -28740,7 +28951,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -28766,7 +28977,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -28778,7 +28989,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">
@@ -28792,7 +29003,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -28804,7 +29015,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264">
@@ -28818,7 +29029,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="D264" t="n">
@@ -28844,7 +29055,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D265" t="n">
@@ -28870,7 +29081,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="D266" t="n">
@@ -28896,19 +29107,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.175</v>
+        <v>1.925</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>o1-mini</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
@@ -28922,19 +29133,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>0.175</v>
+        <v>1.925</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>o1-mini</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="269">
@@ -28948,7 +29159,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="D269" t="n">
@@ -28960,7 +29171,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="270">
@@ -28974,7 +29185,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="D270" t="n">
@@ -28986,7 +29197,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271">
@@ -29000,7 +29211,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -29026,7 +29237,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="D272" t="n">
@@ -29052,7 +29263,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="D273" t="n">
@@ -29064,7 +29275,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274">
@@ -29078,7 +29289,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="D274" t="n">
@@ -29090,7 +29301,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275">
@@ -29104,7 +29315,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="D275" t="n">
@@ -29116,7 +29327,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276">
@@ -29130,7 +29341,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="D276" t="n">
@@ -29156,7 +29367,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="D277" t="n">
@@ -29168,7 +29379,7 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="278">
@@ -29182,7 +29393,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D278" t="n">
@@ -29194,7 +29405,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279">
@@ -29208,7 +29419,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -29234,7 +29445,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="D280" t="n">
@@ -29246,7 +29457,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="281">
@@ -29260,7 +29471,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D281" t="n">
@@ -29272,7 +29483,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="282">
@@ -29286,7 +29497,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="D282" t="n">
@@ -29298,7 +29509,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="283">
@@ -29312,7 +29523,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D283" t="n">
@@ -29324,7 +29535,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="284">
@@ -29338,7 +29549,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="D284" t="n">
@@ -29350,7 +29561,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="285">
@@ -29364,7 +29575,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="D285" t="n">
@@ -29376,7 +29587,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="286">
@@ -29390,7 +29601,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="D286" t="n">
@@ -29416,7 +29627,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -29428,7 +29639,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="288">
@@ -29442,7 +29653,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="D288" t="n">
@@ -29454,7 +29665,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="289">
@@ -29468,7 +29679,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D289" t="n">
@@ -29494,7 +29705,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D290" t="n">
@@ -29506,7 +29717,7 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="291">
@@ -29520,7 +29731,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D291" t="n">
@@ -29528,11 +29739,11 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F291" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="292">
@@ -29546,7 +29757,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -29554,11 +29765,11 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F292" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="293">
@@ -29572,7 +29783,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D293" t="n">
@@ -29584,7 +29795,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="294">
@@ -29598,7 +29809,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D294" t="n">
@@ -29610,7 +29821,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="295">
@@ -29624,7 +29835,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D295" t="n">
@@ -29650,7 +29861,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="D296" t="n">
@@ -29662,7 +29873,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="297">
@@ -29676,7 +29887,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -29688,7 +29899,7 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="298">
@@ -29702,7 +29913,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -29714,7 +29925,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="299">
@@ -29728,7 +29939,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -29740,7 +29951,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="300">
@@ -29754,7 +29965,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D300" t="n">
@@ -29766,7 +29977,7 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="301">
@@ -29780,7 +29991,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -29792,7 +30003,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="302">
@@ -29806,7 +30017,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -29818,7 +30029,7 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="303">
@@ -29832,7 +30043,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D303" t="n">
@@ -29844,7 +30055,7 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="304">
@@ -29858,7 +30069,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -29870,7 +30081,7 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="305">
@@ -29884,7 +30095,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -29896,7 +30107,7 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="306">
@@ -29910,7 +30121,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D306" t="n">
@@ -29922,7 +30133,7 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="307">
@@ -29936,7 +30147,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D307" t="n">
@@ -29948,7 +30159,7 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="308">
@@ -29962,7 +30173,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D308" t="n">
@@ -29974,7 +30185,7 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="309">
@@ -29988,7 +30199,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -30000,7 +30211,7 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="310">
@@ -30014,7 +30225,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D310" t="n">
@@ -30026,7 +30237,7 @@
         </is>
       </c>
       <c r="F310" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="311">
@@ -30040,7 +30251,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D311" t="n">
@@ -30052,7 +30263,7 @@
         </is>
       </c>
       <c r="F311" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="312">
@@ -30066,7 +30277,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D312" t="n">
@@ -30078,7 +30289,7 @@
         </is>
       </c>
       <c r="F312" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="313">
@@ -30092,7 +30303,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D313" t="n">
@@ -30104,7 +30315,7 @@
         </is>
       </c>
       <c r="F313" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="314">
@@ -30118,7 +30329,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D314" t="n">
@@ -30130,7 +30341,7 @@
         </is>
       </c>
       <c r="F314" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="315">
@@ -30144,19 +30355,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="316">
@@ -30170,19 +30381,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="317">
@@ -30196,7 +30407,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D317" t="n">
@@ -30208,7 +30419,7 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="318">
@@ -30222,7 +30433,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -30234,7 +30445,7 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="319">
@@ -30248,7 +30459,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D319" t="n">
@@ -30260,7 +30471,7 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="320">
@@ -30274,7 +30485,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D320" t="n">
@@ -30286,7 +30497,7 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="321">
@@ -30300,7 +30511,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D321" t="n">
@@ -30312,7 +30523,7 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="322">
@@ -30326,7 +30537,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D322" t="n">
@@ -30338,7 +30549,7 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="323">
@@ -30352,7 +30563,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D323" t="n">
@@ -30364,7 +30575,7 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="324">
@@ -30378,7 +30589,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D324" t="n">
@@ -30390,7 +30601,7 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="325">
@@ -30404,7 +30615,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D325" t="n">
@@ -30416,7 +30627,7 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="326">
@@ -30430,7 +30641,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D326" t="n">
@@ -30442,7 +30653,7 @@
         </is>
       </c>
       <c r="F326" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="327">
@@ -30456,7 +30667,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D327" t="n">
@@ -30468,7 +30679,7 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="328">
@@ -30482,7 +30693,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D328" t="n">
@@ -30494,7 +30705,7 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="329">
@@ -30508,7 +30719,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D329" t="n">
@@ -30534,7 +30745,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D330" t="n">
@@ -30546,7 +30757,7 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="331">
@@ -30560,11 +30771,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -30572,7 +30783,7 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="332">
@@ -30586,19 +30797,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>0.1275</v>
+        <v>0.09</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F332" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="333">
@@ -30612,19 +30823,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>0.1275</v>
+        <v>0.11</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>gpt-oss-20b</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="334">
@@ -30638,7 +30849,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -30650,7 +30861,7 @@
         </is>
       </c>
       <c r="F334" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="335">
@@ -30664,7 +30875,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D335" t="n">
@@ -30676,7 +30887,7 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="336">
@@ -30690,7 +30901,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -30702,7 +30913,7 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="337">
@@ -30716,7 +30927,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D337" t="n">
@@ -30728,7 +30939,7 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="338">
@@ -30742,7 +30953,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D338" t="n">
@@ -30754,7 +30965,7 @@
         </is>
       </c>
       <c r="F338" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="339">
@@ -30768,7 +30979,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D339" t="n">
@@ -30780,7 +30991,7 @@
         </is>
       </c>
       <c r="F339" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="340">
@@ -30794,19 +31005,19 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0.11875</v>
+        <v>0.1275</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="341">
@@ -30820,7 +31031,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D341" t="n">
@@ -30832,85 +31043,85 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>1359.023816493652</v>
+        <v>1300.50868831193</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>1.925</v>
+        <v>0.11875</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>o1-mini</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>1359.023816493652</v>
+        <v>1300.50868831193</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>26.25</v>
+        <v>0.1275</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>o1-2024-12-17</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>1359.023816493652</v>
+        <v>1300.50868831193</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>26.25</v>
+        <v>0.1275</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>o1-2024-12-17</t>
+          <t>gpt-oss-20b</t>
         </is>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
     </row>
     <row r="345">
@@ -30924,15 +31135,15 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>26.25</v>
+        <v>1.925</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>o1-2024-12-17</t>
+          <t>o1-mini</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -30950,7 +31161,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D346" t="n">
@@ -30976,7 +31187,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -31002,7 +31213,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -31028,19 +31239,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1.925</v>
+        <v>26.25</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>o3-mini-high</t>
+          <t>o1-2024-12-17</t>
         </is>
       </c>
       <c r="F349" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
@@ -31054,19 +31265,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1.925</v>
+        <v>26.25</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>o3-mini-high</t>
+          <t>o1-2024-12-17</t>
         </is>
       </c>
       <c r="F350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
@@ -31080,19 +31291,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>1.925</v>
+        <v>26.25</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>o3-mini-high</t>
+          <t>o1-2024-12-17</t>
         </is>
       </c>
       <c r="F351" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
@@ -31106,7 +31317,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -31118,7 +31329,7 @@
         </is>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="353">
@@ -31132,7 +31343,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -31144,7 +31355,7 @@
         </is>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="354">
@@ -31158,7 +31369,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -31184,7 +31395,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -31196,7 +31407,7 @@
         </is>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -31210,7 +31421,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -31222,7 +31433,7 @@
         </is>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -31236,7 +31447,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -31244,11 +31455,11 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>o4-mini-2025-04-16</t>
+          <t>o3-mini-high</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -31262,19 +31473,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.925</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>gpt-4.1-mini-2025-04-14</t>
+          <t>o3-mini-high</t>
         </is>
       </c>
       <c r="F358" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -31288,7 +31499,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -31296,11 +31507,11 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>o4-mini-2025-04-16</t>
+          <t>o3-mini-high</t>
         </is>
       </c>
       <c r="F359" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
@@ -31314,19 +31525,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.925</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>gpt-4.1-mini-2025-04-14</t>
+          <t>o4-mini-2025-04-16</t>
         </is>
       </c>
       <c r="F360" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361">
@@ -31340,7 +31551,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -31352,7 +31563,7 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="362">
@@ -31366,19 +31577,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0.175</v>
+        <v>1.925</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>o4-mini-2025-04-16</t>
         </is>
       </c>
       <c r="F362" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -31392,19 +31603,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0.175</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>gpt-4.1-mini-2025-04-14</t>
         </is>
       </c>
       <c r="F363" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="364">
@@ -31418,19 +31629,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.175</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>gemini-2.0-flash-001</t>
+          <t>gpt-4.1-mini-2025-04-14</t>
         </is>
       </c>
       <c r="F364" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="365">
@@ -31444,7 +31655,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -31456,7 +31667,7 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="366">
@@ -31470,7 +31681,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -31482,7 +31693,7 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="367">
@@ -31496,7 +31707,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -31508,7 +31719,7 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="368">
@@ -31522,7 +31733,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -31534,7 +31745,7 @@
         </is>
       </c>
       <c r="F368" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="369">
@@ -31548,7 +31759,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -31560,7 +31771,7 @@
         </is>
       </c>
       <c r="F369" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="370">
@@ -31574,7 +31785,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -31600,7 +31811,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -31608,11 +31819,11 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F371" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="372">
@@ -31626,7 +31837,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -31634,11 +31845,11 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F372" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="373">
@@ -31652,7 +31863,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -31660,11 +31871,11 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
+          <t>gemini-2.0-flash-001</t>
         </is>
       </c>
       <c r="F373" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="374">
@@ -31678,7 +31889,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -31690,7 +31901,7 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="375">
@@ -31704,7 +31915,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -31716,7 +31927,7 @@
         </is>
       </c>
       <c r="F375" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="376">
@@ -31730,7 +31941,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -31742,7 +31953,7 @@
         </is>
       </c>
       <c r="F376" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="377">
@@ -31756,7 +31967,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -31768,7 +31979,7 @@
         </is>
       </c>
       <c r="F377" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="378">
@@ -31782,7 +31993,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -31794,7 +32005,7 @@
         </is>
       </c>
       <c r="F378" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="379">
@@ -31808,7 +32019,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -31820,7 +32031,7 @@
         </is>
       </c>
       <c r="F379" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="380">
@@ -31834,7 +32045,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -31846,7 +32057,7 @@
         </is>
       </c>
       <c r="F380" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="381">
@@ -31860,7 +32071,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D381" t="n">
@@ -31872,7 +32083,7 @@
         </is>
       </c>
       <c r="F381" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="382">
@@ -31886,7 +32097,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D382" t="n">
@@ -31898,7 +32109,7 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="383">
@@ -31912,7 +32123,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -31924,7 +32135,7 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="384">
@@ -31938,7 +32149,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D384" t="n">
@@ -31950,7 +32161,7 @@
         </is>
       </c>
       <c r="F384" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="385">
@@ -31964,7 +32175,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -31976,7 +32187,7 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="386">
@@ -31990,7 +32201,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -32002,7 +32213,7 @@
         </is>
       </c>
       <c r="F386" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="387">
@@ -32016,7 +32227,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -32028,7 +32239,7 @@
         </is>
       </c>
       <c r="F387" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="388">
@@ -32042,7 +32253,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -32054,7 +32265,7 @@
         </is>
       </c>
       <c r="F388" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="389">
@@ -32068,7 +32279,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D389" t="n">
@@ -32080,7 +32291,7 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="390">
@@ -32094,7 +32305,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -32106,7 +32317,7 @@
         </is>
       </c>
       <c r="F390" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="391">
@@ -32120,7 +32331,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -32132,7 +32343,7 @@
         </is>
       </c>
       <c r="F391" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="392">
@@ -32146,7 +32357,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D392" t="n">
@@ -32158,7 +32369,7 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="393">
@@ -32172,7 +32383,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D393" t="n">
@@ -32184,7 +32395,7 @@
         </is>
       </c>
       <c r="F393" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="394">
@@ -32198,7 +32409,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D394" t="n">
@@ -32210,7 +32421,7 @@
         </is>
       </c>
       <c r="F394" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="395">
@@ -32224,19 +32435,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F395" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="396">
@@ -32250,19 +32461,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F396" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="397">
@@ -32276,19 +32487,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>mistral-small-2506</t>
+          <t>gemini-2.5-flash-lite-preview-06-17-thinking</t>
         </is>
       </c>
       <c r="F397" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="398">
@@ -32302,7 +32513,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -32314,7 +32525,7 @@
         </is>
       </c>
       <c r="F398" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="399">
@@ -32328,7 +32539,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -32340,7 +32551,7 @@
         </is>
       </c>
       <c r="F399" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="400">
@@ -32354,7 +32565,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -32366,7 +32577,7 @@
         </is>
       </c>
       <c r="F400" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="401">
@@ -32380,7 +32591,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -32392,7 +32603,7 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="402">
@@ -32406,7 +32617,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -32418,7 +32629,7 @@
         </is>
       </c>
       <c r="F402" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="403">
@@ -32432,7 +32643,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -32444,7 +32655,7 @@
         </is>
       </c>
       <c r="F403" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="404">
@@ -32458,7 +32669,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -32470,7 +32681,7 @@
         </is>
       </c>
       <c r="F404" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="405">
@@ -32484,7 +32695,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D405" t="n">
@@ -32496,7 +32707,7 @@
         </is>
       </c>
       <c r="F405" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="406">
@@ -32510,7 +32721,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D406" t="n">
@@ -32522,7 +32733,7 @@
         </is>
       </c>
       <c r="F406" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="407">
@@ -32536,7 +32747,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D407" t="n">
@@ -32548,7 +32759,7 @@
         </is>
       </c>
       <c r="F407" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="408">
@@ -32562,7 +32773,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D408" t="n">
@@ -32574,7 +32785,7 @@
         </is>
       </c>
       <c r="F408" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="409">
@@ -32588,7 +32799,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D409" t="n">
@@ -32600,7 +32811,7 @@
         </is>
       </c>
       <c r="F409" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="410">
@@ -32614,7 +32825,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D410" t="n">
@@ -32626,7 +32837,7 @@
         </is>
       </c>
       <c r="F410" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="411">
@@ -32640,11 +32851,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -32652,7 +32863,7 @@
         </is>
       </c>
       <c r="F411" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="412">
@@ -32666,11 +32877,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -32678,7 +32889,7 @@
         </is>
       </c>
       <c r="F412" t="n">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="413">
@@ -32692,11 +32903,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -32704,7 +32915,7 @@
         </is>
       </c>
       <c r="F413" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="414">
@@ -32718,11 +32929,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -32730,7 +32941,7 @@
         </is>
       </c>
       <c r="F414" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="415">
@@ -32744,7 +32955,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D415" t="n">
@@ -32756,7 +32967,7 @@
         </is>
       </c>
       <c r="F415" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="416">
@@ -32770,7 +32981,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D416" t="n">
@@ -32782,7 +32993,7 @@
         </is>
       </c>
       <c r="F416" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="417">
@@ -32796,7 +33007,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D417" t="n">
@@ -32808,7 +33019,7 @@
         </is>
       </c>
       <c r="F417" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="418">
@@ -32822,7 +33033,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D418" t="n">
@@ -32834,7 +33045,7 @@
         </is>
       </c>
       <c r="F418" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
     </row>
     <row r="419">
@@ -32848,7 +33059,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D419" t="n">
@@ -32860,7 +33071,7 @@
         </is>
       </c>
       <c r="F419" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="420">
@@ -32874,19 +33085,19 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>0.11875</v>
+        <v>0.15</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F420" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="421">
@@ -32900,7 +33111,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D421" t="n">
@@ -32912,93 +33123,111 @@
         </is>
       </c>
       <c r="F421" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>1491.030286935986</v>
+        <v>1359.023816493652</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>3.4375</v>
+        <v>0.15</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>gemini-2.5-pro</t>
+          <t>mistral-small-2506</t>
         </is>
       </c>
       <c r="F422" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>1491.030286935986</v>
+        <v>1359.023816493652</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
-      <c r="E423" t="inlineStr"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>glm-5.3-flash</t>
+        </is>
+      </c>
       <c r="F423" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>1491.030286935986</v>
+        <v>1359.023816493652</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
-      <c r="E424" t="inlineStr"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>mistral-small-2506</t>
+        </is>
+      </c>
       <c r="F424" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>1491.030286935986</v>
+        <v>1359.023816493652</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr"/>
-      <c r="E425" t="inlineStr"/>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>mistral-small-2506</t>
+        </is>
+      </c>
       <c r="F425" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
     </row>
     <row r="426">
@@ -33012,13 +33241,19 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr"/>
-      <c r="E426" t="inlineStr"/>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>3.4375</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>gemini-2.5-pro</t>
+        </is>
+      </c>
       <c r="F426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -33032,7 +33267,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -33052,7 +33287,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -33072,7 +33307,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -33092,7 +33327,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -33112,7 +33347,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -33132,7 +33367,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -33152,7 +33387,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -33172,19 +33407,13 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="D434" t="n">
-        <v>6</v>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
-        </is>
-      </c>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr"/>
       <c r="F434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
@@ -33198,19 +33427,13 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="D435" t="n">
-        <v>6</v>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
-        </is>
-      </c>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr"/>
       <c r="F435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -33224,19 +33447,13 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="D436" t="n">
-        <v>6</v>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
-        </is>
-      </c>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr"/>
       <c r="F436" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -33250,19 +33467,13 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="D437" t="n">
-        <v>6</v>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
-        </is>
-      </c>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr"/>
       <c r="F437" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
@@ -33276,7 +33487,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="D438" t="n">
@@ -33302,7 +33513,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="D439" t="n">
@@ -33314,7 +33525,7 @@
         </is>
       </c>
       <c r="F439" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440">
@@ -33328,7 +33539,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D440" t="n">
@@ -33340,7 +33551,7 @@
         </is>
       </c>
       <c r="F440" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
@@ -33354,7 +33565,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D441" t="n">
@@ -33366,7 +33577,7 @@
         </is>
       </c>
       <c r="F441" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442">
@@ -33380,7 +33591,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D442" t="n">
@@ -33392,7 +33603,7 @@
         </is>
       </c>
       <c r="F442" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
@@ -33406,7 +33617,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D443" t="n">
@@ -33432,7 +33643,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D444" t="n">
@@ -33458,7 +33669,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -33484,19 +33695,19 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-thinking-32k</t>
+          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
         </is>
       </c>
       <c r="F446" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -33510,19 +33721,19 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-thinking-32k</t>
+          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
         </is>
       </c>
       <c r="F447" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -33536,19 +33747,19 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
         </is>
       </c>
       <c r="F448" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -33562,19 +33773,19 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-sonnet-4-5-20250929-thinking-32k</t>
         </is>
       </c>
       <c r="F449" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -33588,19 +33799,19 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>claude-opus-4-5-20251101-thinking-32k</t>
         </is>
       </c>
       <c r="F450" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451">
@@ -33614,19 +33825,19 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>claude-opus-4-5-20251101-thinking-32k</t>
         </is>
       </c>
       <c r="F451" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="452">
@@ -33640,19 +33851,19 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F452" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="453">
@@ -33666,19 +33877,19 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F453" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="454">
@@ -33692,7 +33903,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -33704,7 +33915,7 @@
         </is>
       </c>
       <c r="F454" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="455">
@@ -33718,7 +33929,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D455" t="n">
@@ -33730,7 +33941,7 @@
         </is>
       </c>
       <c r="F455" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="456">
@@ -33744,7 +33955,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D456" t="n">
@@ -33770,7 +33981,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D457" t="n">
@@ -33796,7 +34007,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D458" t="n">
@@ -33808,7 +34019,7 @@
         </is>
       </c>
       <c r="F458" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="459">
@@ -33822,7 +34033,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D459" t="n">
@@ -33834,7 +34045,7 @@
         </is>
       </c>
       <c r="F459" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="460">
@@ -33848,7 +34059,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D460" t="n">
@@ -33860,7 +34071,7 @@
         </is>
       </c>
       <c r="F460" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="461">
@@ -33874,7 +34085,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D461" t="n">
@@ -33886,7 +34097,7 @@
         </is>
       </c>
       <c r="F461" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="462">
@@ -33900,19 +34111,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>5.625</v>
+        <v>4.5</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>gpt-5.4-high</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F462" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="463">
@@ -33926,19 +34137,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>3.375</v>
+        <v>4.5</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F463" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="464">
@@ -33952,19 +34163,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>qwen3.7-max-preview</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F464" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="465">
@@ -33978,19 +34189,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>3.375</v>
+        <v>4.5</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>gemini-3.5-flash</t>
+          <t>gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="F465" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="466">
@@ -34004,19 +34215,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>3.75</v>
+        <v>5.625</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>qwen3.7-max-preview</t>
+          <t>gpt-5.4-high</t>
         </is>
       </c>
       <c r="F466" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="467">
@@ -34030,7 +34241,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D467" t="n">
@@ -34042,7 +34253,7 @@
         </is>
       </c>
       <c r="F467" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="468">
@@ -34056,19 +34267,19 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>qwen3.7-max-preview</t>
         </is>
       </c>
       <c r="F468" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="469">
@@ -34082,19 +34293,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>2.15</v>
+        <v>3.375</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>gemini-3.5-flash</t>
         </is>
       </c>
       <c r="F469" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="470">
@@ -34108,19 +34319,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>qwen3.7-max-preview</t>
         </is>
       </c>
       <c r="F470" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="471">
@@ -34134,19 +34345,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>2.15</v>
+        <v>3.375</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>glm-5.1</t>
+          <t>gemini-3.5-flash</t>
         </is>
       </c>
       <c r="F471" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="472">
@@ -34160,7 +34371,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -34172,7 +34383,7 @@
         </is>
       </c>
       <c r="F472" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="473">
@@ -34186,19 +34397,19 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>muse-spark-1.1</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="F473" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="474">
@@ -34212,19 +34423,19 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>muse-spark-1.1</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="F474" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="475">
@@ -34238,19 +34449,19 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash-high</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="F475" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="476">
@@ -34264,19 +34475,19 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash-high</t>
+          <t>glm-5.1</t>
         </is>
       </c>
       <c r="F476" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="477">
@@ -34290,19 +34501,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>0.11875</v>
+        <v>2</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>muse-spark-1.1</t>
         </is>
       </c>
       <c r="F477" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="478">
@@ -34316,137 +34527,149 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>0.2375</v>
+        <v>2</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>glm-5.3-flash</t>
+          <t>muse-spark-1.1</t>
         </is>
       </c>
       <c r="F478" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-thinking-32k</t>
+          <t>gemini-3.7-flash-high</t>
         </is>
       </c>
       <c r="F479" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>claude-opus-4-5-20251101-thinking-32k</t>
+          <t>gemini-3.7-flash-high</t>
         </is>
       </c>
       <c r="F480" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr"/>
-      <c r="E481" t="inlineStr"/>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>0.11875</v>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>glm-5.3-flash</t>
+        </is>
+      </c>
       <c r="F481" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr"/>
-      <c r="E482" t="inlineStr"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>glm-5.3-flash</t>
+        </is>
+      </c>
       <c r="F482" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>1516.763815407052</v>
+        <v>1491.030286935986</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>10</v>
+        <v>0.2375</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>glm-5.3-flash</t>
         </is>
       </c>
       <c r="F483" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="484">
@@ -34460,7 +34683,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -34468,11 +34691,11 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-opus-4-5-20251101-thinking-32k</t>
         </is>
       </c>
       <c r="F484" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="485">
@@ -34486,7 +34709,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D485" t="n">
@@ -34494,11 +34717,11 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-opus-4-5-20251101-thinking-32k</t>
         </is>
       </c>
       <c r="F485" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486">
@@ -34512,19 +34735,13 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="D486" t="n">
-        <v>10</v>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>claude-opus-4-6-thinking</t>
-        </is>
-      </c>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr"/>
+      <c r="E486" t="inlineStr"/>
       <c r="F486" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487">
@@ -34538,19 +34755,13 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="D487" t="n">
-        <v>5.625</v>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>gpt-5.4-high</t>
-        </is>
-      </c>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr"/>
+      <c r="E487" t="inlineStr"/>
       <c r="F487" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
@@ -34564,7 +34775,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D488" t="n">
@@ -34590,7 +34801,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D489" t="n">
@@ -34616,7 +34827,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D490" t="n">
@@ -34642,7 +34853,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D491" t="n">
@@ -34668,19 +34879,19 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>10</v>
+        <v>5.625</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>gpt-5.4-high</t>
         </is>
       </c>
       <c r="F492" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -34694,7 +34905,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D493" t="n">
@@ -34702,11 +34913,11 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F493" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494">
@@ -34720,7 +34931,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D494" t="n">
@@ -34732,7 +34943,7 @@
         </is>
       </c>
       <c r="F494" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="495">
@@ -34746,7 +34957,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D495" t="n">
@@ -34754,11 +34965,11 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F495" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="496">
@@ -34772,7 +34983,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -34780,11 +34991,11 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F496" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="497">
@@ -34798,7 +35009,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -34806,11 +35017,11 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F497" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="498">
@@ -34824,7 +35035,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -34832,11 +35043,11 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F498" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="499">
@@ -34850,7 +35061,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D499" t="n">
@@ -34858,7 +35069,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F499" t="n">
@@ -34876,7 +35087,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D500" t="n">
@@ -34888,7 +35099,7 @@
         </is>
       </c>
       <c r="F500" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="501">
@@ -34902,7 +35113,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D501" t="n">
@@ -34928,7 +35139,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="D502" t="n">
@@ -34940,7 +35151,7 @@
         </is>
       </c>
       <c r="F502" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="503">
@@ -34954,7 +35165,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D503" t="n">
@@ -34962,11 +35173,11 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>claude-opus-4-6</t>
+          <t>claude-opus-4-6-thinking</t>
         </is>
       </c>
       <c r="F503" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -34980,7 +35191,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D504" t="n">
@@ -34992,7 +35203,7 @@
         </is>
       </c>
       <c r="F504" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="505">
@@ -35006,7 +35217,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D505" t="n">
@@ -35018,7 +35229,7 @@
         </is>
       </c>
       <c r="F505" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="506">
@@ -35032,7 +35243,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D506" t="n">
@@ -35058,7 +35269,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D507" t="n">
@@ -35070,7 +35281,7 @@
         </is>
       </c>
       <c r="F507" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="508">
@@ -35084,7 +35295,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D508" t="n">
@@ -35096,7 +35307,7 @@
         </is>
       </c>
       <c r="F508" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="509">
@@ -35110,7 +35321,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D509" t="n">
@@ -35118,11 +35329,11 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-thinking</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F509" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="510">
@@ -35136,7 +35347,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D510" t="n">
@@ -35144,11 +35355,11 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F510" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="511">
@@ -35162,7 +35373,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="D511" t="n">
@@ -35170,11 +35381,11 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F511" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="512">
@@ -35188,7 +35399,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D512" t="n">
@@ -35196,7 +35407,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F512" t="n">
@@ -35214,7 +35425,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -35222,11 +35433,167 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>claude-opus-4-6-high</t>
+          <t>claude-opus-4-6</t>
         </is>
       </c>
       <c r="F513" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>10</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-thinking</t>
+        </is>
+      </c>
+      <c r="F514" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>10</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="F515" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>10</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="F516" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>10</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="F517" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>10</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>claude-opus-4-6-high</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>1516.763815407052</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>8</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>claude-opus-5.5-high</t>
+        </is>
+      </c>
+      <c r="F519" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -35246,7 +35613,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Pareto coding frontier export — 2026-09-20</t>
+          <t>Pareto coding frontier export — 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -35270,21 +35637,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Panel weeks: 2024-04-01 → 2026-09-07 (117 weeks)</t>
+          <t>Panel weeks: 2024-04-01 → 2026-09-21 (118 weeks)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Match rate: 198/420 (47.1%)</t>
+          <t>Match rate: 204/428 (47.7%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GPT-6 Astra Max rated on Text/coding from week 2026-09-07; DeepSeek V4.1 Flash is rated on WebDev only</t>
+          <t>Week 2026-09-21 adds Opus 5.5, DeepSeek V4.1 Flash Max, GPT-6 Sol/Luna, Grok 4.7; MiMo v2.6 is unpriced</t>
         </is>
       </c>
     </row>
